--- a/[오름] 마감캘린더_시트양식.xlsx
+++ b/[오름] 마감캘린더_시트양식.xlsx
@@ -1146,11 +1146,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1164,6 +1165,11 @@
           <t>PIN</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1176,6 +1182,7 @@
           <t>1212</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1188,6 +1195,7 @@
           <t>1111</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1200,6 +1208,7 @@
           <t>2222</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1212,6 +1221,7 @@
           <t>3333</t>
         </is>
       </c>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1224,6 +1234,7 @@
           <t>4444</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1236,11 +1247,12 @@
           <t>5555</t>
         </is>
       </c>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>※ PIN은 원장만 알기 — 예시값. 강사 추가 시 index.html CONFIG.teachers에도 추가.</t>
+          <t>※ PIN은 원장만 알기(예시값). 이메일은 리마인드용 — 비우면 그 사람은 메일 안 감. 가경T가 '전체 미이행 요약' 수신.</t>
         </is>
       </c>
     </row>
@@ -1255,11 +1267,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1273,6 +1286,11 @@
           <t>PIN</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1285,6 +1303,7 @@
           <t>7001</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1297,6 +1316,7 @@
           <t>7002</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1309,6 +1329,7 @@
           <t>7003</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1321,6 +1342,7 @@
           <t>7004</t>
         </is>
       </c>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1333,6 +1355,7 @@
           <t>7005</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1345,6 +1368,7 @@
           <t>7006</t>
         </is>
       </c>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1357,6 +1381,7 @@
           <t>7007</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1369,6 +1394,7 @@
           <t>7010</t>
         </is>
       </c>
+      <c r="C9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1381,11 +1407,12 @@
           <t>7011</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>※ 조교는 '전체'에 미포함. 담당 칸에 이름 직접 또는 '조교전체'. 추가 시 CONFIG.assistants에도 추가.</t>
+          <t>※ 조교는 '전체'에 미포함. 담당 칸에 이름 직접 또는 '조교전체'. 이메일 입력 시 리마인드 발송.</t>
         </is>
       </c>
     </row>

--- a/[오름] 마감캘린더_시트양식.xlsx
+++ b/[오름] 마감캘린더_시트양식.xlsx
@@ -1146,12 +1146,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1168,6 +1169,11 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>이메일</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>전화번호</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1273,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1289,6 +1296,11 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>이메일</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>전화번호</t>
         </is>
       </c>
     </row>
